--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
   <si>
     <t>Filename</t>
   </si>
@@ -808,688 +808,703 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9947,0.0001,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.9927,0.0000,0.0004,0.0056</t>
-  </si>
-  <si>
-    <t>0.0859,0.0003,0.0001,0.9789</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9947,0.0001,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0189,0.0002,0.0003,0.9942</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9985,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9043,0.0056,0.0830,0.0006</t>
+  </si>
+  <si>
+    <t>0.0484,0.0013,0.9531,0.0008</t>
+  </si>
+  <si>
+    <t>0.0223,0.0026,0.9850,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0005,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.4756,0.0011,0.5633,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7712,0.0007,0.1531,0.0048</t>
+  </si>
+  <si>
+    <t>0.2182,0.0018,0.7827,0.0019</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0004,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.1516,0.0002,0.9047,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.9574,0.0275,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9179,0.0150,0.0384,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9998,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9968,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0024,0.0052,0.0019</t>
+  </si>
+  <si>
+    <t>0.9072,0.1168,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.4261,0.8913,0.0021</t>
+  </si>
+  <si>
+    <t>0.0038,0.0085,0.8899,0.0596</t>
+  </si>
+  <si>
+    <t>0.0003,0.0196,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.0003,0.9926,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.2804,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.0059,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0310,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9960,0.0309,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0074,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0156,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0013,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9998,0.0080</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9896,0.0110,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9917,0.9891,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9979,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9992,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9128,0.0021,0.1041,0.0001</t>
+  </si>
+  <si>
+    <t>0.6255,0.0244,0.2350,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9912,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.8403,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9116,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.0061,0.9960</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.0290,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9896,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9878,0.9945,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1827,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9649,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9853,0.1384,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0001,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9376,0.1179,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9805,0.0003,0.0141,0.0003</t>
+  </si>
+  <si>
+    <t>0.9534,0.0019,0.0315,0.0001</t>
+  </si>
+  <si>
+    <t>0.9045,0.0026,0.0721,0.0006</t>
+  </si>
+  <si>
+    <t>0.7432,0.0007,0.2374,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0105,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0215,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0003,0.0155</t>
+  </si>
+  <si>
+    <t>0.0000,0.9931,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9852,0.0141,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.8016,0.2103,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0005,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9756,0.0010,0.0174,0.0004</t>
-  </si>
-  <si>
-    <t>0.0126,0.0026,0.9825,0.0010</t>
-  </si>
-  <si>
-    <t>0.0163,0.0020,0.9891,0.0001</t>
-  </si>
-  <si>
-    <t>0.0196,0.0034,0.9703,0.0015</t>
-  </si>
-  <si>
-    <t>0.9579,0.0016,0.0321,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9973,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2729,0.0002,0.6987,0.0034</t>
-  </si>
-  <si>
-    <t>0.0321,0.0015,0.9660,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0105,0.0009,0.9882,0.0002</t>
-  </si>
-  <si>
-    <t>0.0229,0.0001,0.9884,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0003,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9552,0.0301,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.9020,0.0301,0.0351,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0030,0.9994,0.0038</t>
-  </si>
-  <si>
-    <t>0.0355,0.9563,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0007,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.6628,0.4625,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9952,0.0743,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.1637,0.9390,0.0009</t>
-  </si>
-  <si>
-    <t>0.0076,0.0267,0.9189,0.0182</t>
-  </si>
-  <si>
-    <t>0.0009,0.0028,0.9970,0.0005</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.9975,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0123,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9977,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.1131,0.0003,0.9761</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.0048,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0875,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0195,0.0006,0.9874,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0011,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0030</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.8774,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.9917,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.9987,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9633,0.0022,0.0310,0.0001</t>
-  </si>
-  <si>
-    <t>0.3444,0.0113,0.6091,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.6926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0043,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.5470,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0003,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9982,0.0187,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9873,0.9515,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9478,0.9065,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9885,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9778,0.9509,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0036,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.9886,0.0002,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9982,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9399,0.1023,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0338,0.0013,0.9618,0.0018</t>
-  </si>
-  <si>
-    <t>0.9810,0.0037,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.0684,0.0130,0.8807,0.0013</t>
-  </si>
-  <si>
-    <t>0.2527,0.0010,0.7124,0.0053</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.0005,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0156,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9662,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.7298,0.3113,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.6349,0.3441,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.9929,0.0019,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
+    <t>0.9968,0.0007,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0283,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0980,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9931,0.0002,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.0408,0.0015,0.9582,0.0013</t>
+  </si>
+  <si>
+    <t>0.3117,0.0001,0.8360,0.0002</t>
+  </si>
+  <si>
+    <t>0.8634,0.0053,0.1062,0.0026</t>
+  </si>
+  <si>
+    <t>0.0222,0.0000,0.0000,0.9966</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.6529,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0312,0.9654,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.4094,0.6063,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0092,0.0004,0.0001,0.9968</t>
+  </si>
+  <si>
+    <t>0.0182,0.0054,0.9711,0.0092</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.9760,0.0301,0.0010</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0130,0.9773,0.0025,0.0014</t>
+  </si>
+  <si>
+    <t>0.9961,0.0004,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9801,0.0124,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9987,0.0001,0.0003,0.0003</t>
   </si>
   <si>
-    <t>0.0009,0.0489,0.9895,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0276,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0982,0.0039,0.9124,0.0005</t>
-  </si>
-  <si>
-    <t>0.9667,0.0001,0.0456,0.0001</t>
-  </si>
-  <si>
-    <t>0.9793,0.0022,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.0762,0.0000,0.0002,0.9856</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.4021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.9953,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9938,0.0034,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.9978,0.0036</t>
-  </si>
-  <si>
-    <t>0.9942,0.0000,0.0004,0.0055</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0000,0.0023</t>
-  </si>
-  <si>
-    <t>0.0070,0.9738,0.0125,0.0046</t>
-  </si>
-  <si>
-    <t>0.9951,0.0007,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1343,0.4297,0.0433,0.0121</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0743,0.9416,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9781,0.0176,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.8261,0.1687,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.8710,0.1253,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.9132,0.0286,0.0376,0.0012</t>
-  </si>
-  <si>
-    <t>0.9906,0.0093,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8751,0.0929,0.0104,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9697,0.0032,0.0010,0.0052</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0323,0.9806,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0110,0.9924,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0059,0.0007,0.9926,0.0004</t>
-  </si>
-  <si>
-    <t>0.0045,0.0004,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0021,0.9940,0.0009</t>
-  </si>
-  <si>
-    <t>0.3155,0.0048,0.6355,0.0003</t>
-  </si>
-  <si>
-    <t>0.2340,0.0266,0.5603,0.0001</t>
-  </si>
-  <si>
-    <t>0.9833,0.0034,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9268,0.0054,0.0269,0.0041</t>
-  </si>
-  <si>
-    <t>0.0406,0.0058,0.9539,0.0010</t>
-  </si>
-  <si>
-    <t>0.8180,0.2282,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.9940,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.9589,0.0475,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0143,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0103,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9223,0.0003,0.0097,0.0266</t>
-  </si>
-  <si>
-    <t>0.3165,0.0009,0.7147,0.0015</t>
-  </si>
-  <si>
-    <t>0.2309,0.0016,0.8466,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0043,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0074,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0019,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0084,0.9952,0.0005</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0027,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0013,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0335,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.0070,0.8429,0.1370,0.0011</t>
-  </si>
-  <si>
-    <t>0.9963,0.0001,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.0008,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7992,0.9986,0.0000</t>
+    <t>0.9987,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9792,0.0120,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.8944,0.1164,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9044,0.0749,0.0113,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.0070,0.9933,0.0008</t>
+  </si>
+  <si>
+    <t>0.9960,0.0027,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9909,0.0035,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9655,0.0187,0.0069,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0005</t>
+  </si>
+  <si>
+    <t>0.9171,0.0302,0.0054,0.0045</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0038,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0153,0.9886,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0060,0.9997,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.4065,0.0008,0.7011,0.0004</t>
-  </si>
-  <si>
-    <t>0.0870,0.0003,0.9388,0.0009</t>
-  </si>
-  <si>
-    <t>0.9735,0.0002,0.0230,0.0011</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0028,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0024,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0087,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0096,0.0076,0.9747,0.0013</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0122,0.0004,0.9851,0.0020</t>
-  </si>
-  <si>
-    <t>0.6884,0.0013,0.2457,0.0009</t>
-  </si>
-  <si>
-    <t>0.0238,0.0004,0.9765,0.0008</t>
-  </si>
-  <si>
-    <t>0.1056,0.0002,0.0008,0.9674</t>
-  </si>
-  <si>
-    <t>0.0039,0.0094,0.0004,0.9954</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.0002,0.9992</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9921,0.0005,0.0003,0.0020</t>
+    <t>0.0003,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.1561,0.0019,0.8581,0.0010</t>
+  </si>
+  <si>
+    <t>0.0029,0.0004,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0119,0.0021,0.9863,0.0007</t>
+  </si>
+  <si>
+    <t>0.0496,0.9002,0.0145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0320,0.3291,0.4486,0.0002</t>
+  </si>
+  <si>
+    <t>0.9811,0.0032,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.8901,0.0025,0.0624,0.0067</t>
+  </si>
+  <si>
+    <t>0.0647,0.0048,0.9348,0.0005</t>
+  </si>
+  <si>
+    <t>0.4848,0.6155,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0473,0.9507,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0026,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9049,0.1517,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4319,0.7478,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9793,0.0183,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9876,0.0005,0.0080,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9459,0.0006,0.0426,0.0011</t>
+  </si>
+  <si>
+    <t>0.5565,0.0013,0.5448,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9982,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0050,0.9918,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.0020,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0254,0.9800,0.0006</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0011,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0344,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0135,0.0418,0.9373,0.0014</t>
+  </si>
+  <si>
+    <t>0.9939,0.0004,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.0001,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0031,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2439,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0010,0.9973,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0023,0.9933,0.0010</t>
+  </si>
+  <si>
+    <t>0.9905,0.0001,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.7858,0.0002,0.3237,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0001,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0015,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0013,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0015,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0050,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0044,0.9935,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0161,0.0005,0.9825,0.0009</t>
+  </si>
+  <si>
+    <t>0.1888,0.0046,0.7327,0.0028</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9966,0.0016</t>
+  </si>
+  <si>
+    <t>0.4811,0.0001,0.0064,0.5891</t>
+  </si>
+  <si>
+    <t>0.0004,0.0298,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0126,0.0000,0.0003,0.9958</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.7466,0.0050,0.0011,0.1952</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1890,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1904,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1932,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2058,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2072,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,7 +2086,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2100,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2096,10 +2111,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2156,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2212,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,7 +2254,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,7 +2296,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,7 +2310,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2338,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2366,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,7 +2380,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2394,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,7 +2408,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2436,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2464,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2492,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2506,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2548,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2632,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2646,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2660,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2674,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2688,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2702,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2716,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2730,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2744,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2758,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2772,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2786,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2800,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2814,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2828,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2842,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,10 +2853,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2870,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2898,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2912,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,7 +2926,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2982,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2996,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +3010,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,7 +3024,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3052,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3048,10 +3063,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3080,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,10 +3091,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3122,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3136,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3247,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>359</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>358</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,7 +3472,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,10 +3483,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,7 +3500,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,10 +3511,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3525,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3542,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3556,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3598,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3626,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3681,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3695,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3724,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3723,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,7 +3766,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3765,7 +3780,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3794,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3821,7 +3836,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3832,10 +3847,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3849,7 +3864,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3892,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3906,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3920,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,10 +3931,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3948,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>274</v>
+        <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3962,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,10 +3987,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +4004,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4003,7 +4018,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>273</v>
+        <v>386</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4046,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,7 +4088,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,10 +4127,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,10 +4155,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>406</v>
+        <v>276</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>273</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4308,10 +4323,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>320</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4535,7 +4550,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,10 +4561,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,10 +4575,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,7 +4592,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4606,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4620,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4616,10 +4631,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4662,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4676,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,10 +4687,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4704,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4732,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,10 +4743,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,10 +4757,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4802,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4816,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4830,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4858,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>352</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4914,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4928,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>379</v>
+        <v>464</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4967,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5008,10 +5023,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5068,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5092,10 +5107,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,10 +5121,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5138,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>476</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5292,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5334,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,10 +5345,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5376,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5404,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5418,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5432,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,7 +5446,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
